--- a/ASTRA_LERNAEA/Equilibrage.xlsx
+++ b/ASTRA_LERNAEA/Equilibrage.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simon\Desktop\Aux_Armes\ASTRA_LERNAEA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simon\Desktop\Aux_Armes\space-wargames\ASTRA_LERNAEA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64483A94-F619-4D34-90F9-BD33890B4994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B3DEBCA-8516-46BA-9DD0-580AC67DE88E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{454E5E54-5BEC-4760-B38D-ACF2FA6D7C7D}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="85">
   <si>
     <t>Niveau\Bâtiment</t>
   </si>
@@ -241,6 +241,108 @@
   </si>
   <si>
     <t>Comportement\Unités</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Bonus:</t>
+  </si>
+  <si>
+    <t>Bonus\Unités</t>
+  </si>
+  <si>
+    <t>Dégâts</t>
+  </si>
+  <si>
+    <t>Soin</t>
+  </si>
+  <si>
+    <t>Défense</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <r>
+      <t>La Néolithe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>L'Ilektraérium</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>La Vitriolite</t>
+  </si>
+  <si>
+    <t>Utiliter des ressources :</t>
+  </si>
+  <si>
+    <r>
+      <t>L'Integrium</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>L'Héliosium</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Paie les Points de Vie (HP) et l'Armure.</t>
+  </si>
+  <si>
+    <t>Paie la Mobilité et la technologie de base.</t>
+  </si>
+  <si>
+    <t>Paie les Munitions et la Portée.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Paie les Points d'Action (PA), les Infections et la Furtivité.</t>
+  </si>
+  <si>
+    <t>Paie les Boucliers et les Soins lourds.</t>
   </si>
 </sst>
 </file>
@@ -407,7 +509,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -471,8 +573,17 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -817,6 +928,15 @@
     <col min="5" max="5" width="16.26953125" customWidth="1"/>
     <col min="6" max="6" width="30.6328125" customWidth="1"/>
     <col min="7" max="7" width="18.08984375" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" customWidth="1"/>
+    <col min="10" max="10" width="12.453125" customWidth="1"/>
+    <col min="11" max="11" width="12.7265625" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="13.08984375" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="20.1796875" customWidth="1"/>
+    <col min="16" max="16" width="21" customWidth="1"/>
+    <col min="17" max="17" width="49.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
@@ -1846,7 +1966,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32DAF56C-0463-4702-8396-04D4B0C718DA}">
-  <dimension ref="A1:AA25"/>
+  <dimension ref="A1:AA35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.08984375" customWidth="1"/>
@@ -1861,6 +1981,8 @@
     <col min="11" max="11" width="16.81640625" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
     <col min="15" max="15" width="24.54296875" customWidth="1"/>
+    <col min="18" max="18" width="13.08984375" customWidth="1"/>
+    <col min="22" max="22" width="16.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.35">
@@ -1878,10 +2000,10 @@
       </c>
     </row>
     <row r="3" spans="1:27" ht="21" x14ac:dyDescent="0.5">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="O3" s="30" t="s">
+      <c r="O3" s="29" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2001,18 +2123,18 @@
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="25"/>
+      <c r="M6" s="25"/>
       <c r="O6" s="3" t="s">
         <v>7</v>
       </c>
@@ -2033,18 +2155,18 @@
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
       <c r="O7" s="3" t="s">
         <v>8</v>
       </c>
@@ -2065,18 +2187,20 @@
       <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="27"/>
-      <c r="K8" s="27"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
+      <c r="B8" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="25"/>
       <c r="O8" s="3" t="s">
         <v>11</v>
       </c>
@@ -2097,18 +2221,20 @@
       <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26"/>
+      <c r="B9" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
       <c r="O9" s="3" t="s">
         <v>10</v>
       </c>
@@ -2129,18 +2255,20 @@
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="27"/>
-      <c r="K10" s="27"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
+      <c r="B10" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
       <c r="O10" s="3" t="s">
         <v>9</v>
       </c>
@@ -2273,387 +2401,975 @@
       <c r="A14" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="26"/>
-      <c r="M14" s="26"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="25"/>
       <c r="O14" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="P14" s="28"/>
-      <c r="Q14" s="28"/>
-      <c r="R14" s="28"/>
-      <c r="S14" s="28"/>
-      <c r="T14" s="27"/>
-      <c r="U14" s="27"/>
-      <c r="V14" s="27"/>
-      <c r="W14" s="27"/>
-      <c r="X14" s="26"/>
-      <c r="Y14" s="26"/>
-      <c r="Z14" s="26"/>
-      <c r="AA14" s="26"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="23"/>
+      <c r="T14" s="24"/>
+      <c r="U14" s="24"/>
+      <c r="V14" s="24"/>
+      <c r="W14" s="24"/>
+      <c r="X14" s="25"/>
+      <c r="Y14" s="25"/>
+      <c r="Z14" s="25"/>
+      <c r="AA14" s="25"/>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="26"/>
+      <c r="B15" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15" s="30"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="J15" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="K15" s="24"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="25"/>
       <c r="O15" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="P15" s="28"/>
-      <c r="Q15" s="28"/>
-      <c r="R15" s="28"/>
-      <c r="S15" s="28"/>
-      <c r="T15" s="27"/>
-      <c r="U15" s="27"/>
-      <c r="V15" s="27"/>
-      <c r="W15" s="27"/>
-      <c r="X15" s="26"/>
-      <c r="Y15" s="26"/>
-      <c r="Z15" s="26"/>
-      <c r="AA15" s="26"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="R15" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="S15" s="23"/>
+      <c r="T15" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="U15" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="V15" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="W15" s="24"/>
+      <c r="X15" s="25"/>
+      <c r="Y15" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z15" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA15" s="25"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="27"/>
-      <c r="L16" s="26"/>
-      <c r="M16" s="26"/>
+      <c r="B16" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="H16" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I16" s="23"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="L16" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="M16" s="25" t="s">
+        <v>67</v>
+      </c>
       <c r="O16" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="P16" s="28"/>
-      <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
-      <c r="S16" s="28"/>
-      <c r="T16" s="27"/>
-      <c r="U16" s="27"/>
-      <c r="V16" s="27"/>
-      <c r="W16" s="27"/>
-      <c r="X16" s="26"/>
-      <c r="Y16" s="26"/>
-      <c r="Z16" s="26"/>
-      <c r="AA16" s="26"/>
+      <c r="P16" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q16" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="R16" s="23"/>
+      <c r="S16" s="23"/>
+      <c r="T16" s="24"/>
+      <c r="U16" s="24"/>
+      <c r="V16" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="W16" s="24"/>
+      <c r="X16" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y16" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z16" s="25"/>
+      <c r="AA16" s="25"/>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="29"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="27"/>
-      <c r="K17" s="27"/>
-      <c r="L17" s="26"/>
-      <c r="M17" s="26"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G17" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="K17" s="24"/>
+      <c r="L17" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="M17" s="25"/>
       <c r="O17" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="P17" s="28"/>
-      <c r="Q17" s="28"/>
-      <c r="R17" s="28"/>
-      <c r="S17" s="28"/>
-      <c r="T17" s="27"/>
-      <c r="U17" s="27"/>
-      <c r="V17" s="27"/>
-      <c r="W17" s="27"/>
-      <c r="X17" s="26"/>
-      <c r="Y17" s="26"/>
-      <c r="Z17" s="26"/>
-      <c r="AA17" s="26"/>
+      <c r="P17" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
+      <c r="S17" s="23"/>
+      <c r="T17" s="24"/>
+      <c r="U17" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="V17" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="W17" s="24"/>
+      <c r="X17" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y17" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z17" s="25"/>
+      <c r="AA17" s="25"/>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="29"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="27"/>
-      <c r="K18" s="27"/>
-      <c r="L18" s="26"/>
-      <c r="M18" s="26"/>
+      <c r="B18" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G18" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="J18" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="K18" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="L18" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="M18" s="25" t="s">
+        <v>67</v>
+      </c>
       <c r="O18" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="P18" s="28"/>
-      <c r="Q18" s="28"/>
-      <c r="R18" s="28"/>
-      <c r="S18" s="28"/>
-      <c r="T18" s="27"/>
-      <c r="U18" s="27"/>
-      <c r="V18" s="27"/>
-      <c r="W18" s="27"/>
-      <c r="X18" s="26"/>
-      <c r="Y18" s="26"/>
-      <c r="Z18" s="26"/>
-      <c r="AA18" s="26"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="R18" s="23"/>
+      <c r="S18" s="23"/>
+      <c r="T18" s="24"/>
+      <c r="U18" s="24"/>
+      <c r="V18" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="W18" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="X18" s="25"/>
+      <c r="Y18" s="25"/>
+      <c r="Z18" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA18" s="25" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="27"/>
-      <c r="L19" s="26"/>
-      <c r="M19" s="26"/>
+      <c r="B19" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="F19" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G19" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I19" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="J19" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="K19" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="L19" s="25"/>
+      <c r="M19" s="25"/>
       <c r="O19" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="P19" s="28"/>
-      <c r="Q19" s="28"/>
-      <c r="R19" s="28"/>
-      <c r="S19" s="28"/>
-      <c r="T19" s="27"/>
-      <c r="U19" s="27"/>
-      <c r="V19" s="27"/>
-      <c r="W19" s="27"/>
-      <c r="X19" s="26"/>
-      <c r="Y19" s="26"/>
-      <c r="Z19" s="26"/>
-      <c r="AA19" s="26"/>
+      <c r="P19" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q19" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="R19" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="S19" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="T19" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="U19" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="V19" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="W19" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="X19" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y19" s="25"/>
+      <c r="Z19" s="25"/>
+      <c r="AA19" s="25"/>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27"/>
-      <c r="L20" s="26"/>
-      <c r="M20" s="26"/>
+      <c r="B20" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G20" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I20" s="23"/>
+      <c r="J20" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="K20" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="L20" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="M20" s="25" t="s">
+        <v>67</v>
+      </c>
       <c r="O20" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="P20" s="28"/>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28"/>
-      <c r="T20" s="27"/>
-      <c r="U20" s="27"/>
-      <c r="V20" s="27"/>
-      <c r="W20" s="27"/>
-      <c r="X20" s="26"/>
-      <c r="Y20" s="26"/>
-      <c r="Z20" s="26"/>
-      <c r="AA20" s="26"/>
+      <c r="P20" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q20" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="R20" s="23"/>
+      <c r="S20" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="T20" s="24"/>
+      <c r="U20" s="24"/>
+      <c r="V20" s="24"/>
+      <c r="W20" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="X20" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y20" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z20" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA20" s="25" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="29"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="27"/>
-      <c r="K21" s="27"/>
-      <c r="L21" s="26"/>
-      <c r="M21" s="26"/>
+      <c r="B21" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I21" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="J21" s="24"/>
+      <c r="K21" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="L21" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="M21" s="25" t="s">
+        <v>67</v>
+      </c>
       <c r="O21" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="P21" s="28"/>
-      <c r="Q21" s="28"/>
-      <c r="R21" s="28"/>
-      <c r="S21" s="28"/>
-      <c r="T21" s="27"/>
-      <c r="U21" s="27"/>
-      <c r="V21" s="27"/>
-      <c r="W21" s="27"/>
-      <c r="X21" s="26"/>
-      <c r="Y21" s="26"/>
-      <c r="Z21" s="26"/>
-      <c r="AA21" s="26"/>
+      <c r="P21" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q21" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="R21" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="S21" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="T21" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="U21" s="24"/>
+      <c r="V21" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="W21" s="24"/>
+      <c r="X21" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y21" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z21" s="25"/>
+      <c r="AA21" s="25" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B22" s="29"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="27"/>
-      <c r="K22" s="27"/>
-      <c r="L22" s="26"/>
-      <c r="M22" s="26"/>
+      <c r="B22" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="H22" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I22" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="J22" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="K22" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="L22" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="M22" s="25" t="s">
+        <v>67</v>
+      </c>
       <c r="O22" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="P22" s="28"/>
-      <c r="Q22" s="28"/>
-      <c r="R22" s="28"/>
-      <c r="S22" s="28"/>
-      <c r="T22" s="27"/>
-      <c r="U22" s="27"/>
-      <c r="V22" s="27"/>
-      <c r="W22" s="27"/>
-      <c r="X22" s="26"/>
-      <c r="Y22" s="26"/>
-      <c r="Z22" s="26"/>
-      <c r="AA22" s="26"/>
+      <c r="P22" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q22" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="R22" s="23"/>
+      <c r="S22" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="T22" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="U22" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="V22" s="24"/>
+      <c r="W22" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="X22" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y22" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z22" s="25"/>
+      <c r="AA22" s="25"/>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="26"/>
-      <c r="M23" s="26"/>
+      <c r="B23" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="E23" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G23" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="J23" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="K23" s="24"/>
+      <c r="L23" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="M23" s="25"/>
       <c r="O23" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="P23" s="28"/>
-      <c r="Q23" s="28"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="28"/>
-      <c r="T23" s="27"/>
-      <c r="U23" s="27"/>
-      <c r="V23" s="27"/>
-      <c r="W23" s="27"/>
-      <c r="X23" s="26"/>
-      <c r="Y23" s="26"/>
-      <c r="Z23" s="26"/>
-      <c r="AA23" s="26"/>
+      <c r="P23" s="23"/>
+      <c r="Q23" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="R23" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="S23" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="T23" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="U23" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="V23" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="W23" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="X23" s="25"/>
+      <c r="Y23" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z23" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA23" s="25" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B24" s="29"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="27"/>
-      <c r="L24" s="26"/>
-      <c r="M24" s="26"/>
+      <c r="B24" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G24" s="30"/>
+      <c r="H24" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I24" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="J24" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="K24" s="24"/>
+      <c r="L24" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="M24" s="25" t="s">
+        <v>67</v>
+      </c>
       <c r="O24" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="P24" s="28"/>
-      <c r="Q24" s="28"/>
-      <c r="R24" s="28"/>
-      <c r="S24" s="28"/>
-      <c r="T24" s="27"/>
-      <c r="U24" s="27"/>
-      <c r="V24" s="27"/>
-      <c r="W24" s="27"/>
-      <c r="X24" s="26"/>
-      <c r="Y24" s="26"/>
-      <c r="Z24" s="26"/>
-      <c r="AA24" s="26"/>
+      <c r="P24" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q24" s="23"/>
+      <c r="R24" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="S24" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="T24" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="U24" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="V24" s="24"/>
+      <c r="W24" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="X24" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y24" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z24" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA24" s="25" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B25" s="29"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="27"/>
-      <c r="L25" s="26"/>
-      <c r="M25" s="26"/>
+      <c r="B25" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G25" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="H25" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="I25" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="J25" s="24"/>
+      <c r="K25" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="L25" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="M25" s="25" t="s">
+        <v>67</v>
+      </c>
       <c r="O25" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="P25" s="28"/>
-      <c r="Q25" s="28"/>
-      <c r="R25" s="28"/>
-      <c r="S25" s="28"/>
-      <c r="T25" s="27"/>
-      <c r="U25" s="27"/>
-      <c r="V25" s="27"/>
-      <c r="W25" s="27"/>
-      <c r="X25" s="26"/>
-      <c r="Y25" s="26"/>
-      <c r="Z25" s="26"/>
-      <c r="AA25" s="26"/>
+      <c r="P25" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q25" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="R25" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="S25" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="T25" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="U25" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="V25" s="24"/>
+      <c r="W25" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="X25" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y25" s="25"/>
+      <c r="Z25" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA25" s="25"/>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="O27" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="5"/>
+      <c r="S27" s="5"/>
+      <c r="T27" s="5"/>
+      <c r="U27" s="5"/>
+      <c r="V27" s="5"/>
+      <c r="W27" s="5"/>
+      <c r="X27" s="5"/>
+      <c r="Y27" s="5"/>
+      <c r="Z27" s="5"/>
+      <c r="AA27" s="5"/>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="O28" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="P28" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q28" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="R28" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="S28" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="T28" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="U28" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="V28" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="W28" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="X28" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y28" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z28" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA28" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="O29" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="P29" s="23"/>
+      <c r="Q29" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="R29" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="S29" s="23"/>
+      <c r="T29" s="24"/>
+      <c r="U29" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="V29" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="W29" s="24"/>
+      <c r="X29" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y29" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z29" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA29" s="25"/>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A30" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" s="31"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="O30" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P30" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q30" s="23"/>
+      <c r="R30" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="S30" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="T30" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="U30" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="V30" s="24"/>
+      <c r="W30" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="X30" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y30" s="25"/>
+      <c r="Z30" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA30" s="25" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A31" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="B31" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="37"/>
+      <c r="O31" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="P31" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q31" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="T31" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="U31" s="24"/>
+      <c r="V31" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="W31" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="X31" s="25"/>
+      <c r="Y31" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z31" s="25"/>
+      <c r="AA31" s="25" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A32" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" s="37"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="37"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" s="37"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="37"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="B34" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35" s="37"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="37"/>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B31:E31"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>